--- a/plantillas/Base_Empleados.xlsx
+++ b/plantillas/Base_Empleados.xlsx
@@ -40,8 +40,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3B73"/>
-        <bgColor rgb="001F3B73"/>
+        <fgColor rgb="001B3F6E"/>
+        <bgColor rgb="001B3F6E"/>
       </patternFill>
     </fill>
   </fills>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -436,8 +436,10 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,6 +483,16 @@
           <t>Correo</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Cuenta bancaria</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Ingreso promedio variable</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -516,6 +528,14 @@
         <is>
           <t>empleado@email.com</t>
         </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Bco Nacional Cta Ahorros #000111222</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -529,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -552,21 +572,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nombre, Documento, Cargo, Salario y Fecha ingreso son obligatorios.</t>
+          <t>Nombre, Documento, Cargo, Salario y Fecha ingreso son OBLIGATORIOS.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Fecha ingreso y Fecha retiro en formato dd/mm/aaaa.</t>
+          <t>Fechas en formato dd/mm/aaaa.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Deja 'Fecha retiro' vacía si el empleado sigue activo.</t>
+          <t>Deja Fecha retiro vacía si el empleado sigue activo.</t>
         </is>
       </c>
     </row>
@@ -580,7 +600,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>El Salario debe ser un número, sin puntos ni signos ($).</t>
+          <t>Salario: número sin puntos ni signos ($).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Cuenta bancaria: para liquidaciones (ej. Bancolombia Ahorros #123456).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ingreso promedio variable: 0 si no aplica, o el valor promedio mensual.</t>
         </is>
       </c>
     </row>
